--- a/Excel/Cash_Management_Entry.xlsx
+++ b/Excel/Cash_Management_Entry.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emon\Desktop\AccountsPayableProd\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RPA\Desktop\AccountsPayableProd_Citi\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FBC66D-CDA2-41E6-B32D-06A99E5278A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33109286-C67F-4868-8E13-E8F358470096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EVENT1" sheetId="2" r:id="rId1"/>
+    <sheet name="CITI" sheetId="2" r:id="rId1"/>
     <sheet name="EVENT" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="57">
   <si>
     <t>SCB_Expense_Type</t>
   </si>
@@ -88,41 +91,122 @@
     <t>COMMISSION- OTT</t>
   </si>
   <si>
-    <t>PAYMENT OF IMPORT BILL</t>
+    <t>CORR BANK'S INT</t>
+  </si>
+  <si>
+    <t>UPAS Liabilitie</t>
+  </si>
+  <si>
+    <t>GRN</t>
+  </si>
+  <si>
+    <t>FUNDS REMITTED</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>15303010001:27201020010</t>
+  </si>
+  <si>
+    <t>45101010013:41101096008</t>
+  </si>
+  <si>
+    <t>CITI_Expense_Type</t>
+  </si>
+  <si>
+    <t>CITI_Supplier_Site_Name</t>
+  </si>
+  <si>
+    <t>CITI_Type</t>
+  </si>
+  <si>
+    <t>ACCEPTANCE COMMISSION CHARGE</t>
+  </si>
+  <si>
+    <t>NULC ISSUANCE COMMISSION</t>
+  </si>
+  <si>
+    <t>LC ISSUANCE COMMISSION</t>
+  </si>
+  <si>
+    <t>LC AMENDMENT COMMISSION</t>
+  </si>
+  <si>
+    <t>ENDORSEMENT FEE</t>
+  </si>
+  <si>
+    <t>STAMP CHARGES COLLECTED</t>
+  </si>
+  <si>
+    <t>NOC ISSUANCE CHARGE</t>
+  </si>
+  <si>
+    <t>OUTGOING RTGS MONTHLY CHARGE</t>
+  </si>
+  <si>
+    <t>EXP CERTIFICATION</t>
+  </si>
+  <si>
+    <t>PRC  ISSUANCE CHARGE</t>
+  </si>
+  <si>
+    <t>FREIGHT CERTIFICATE ISSUANCE CHARGE</t>
+  </si>
+  <si>
+    <t>PRINCIPAL LIQUIDATION</t>
   </si>
   <si>
     <t>Prepayment</t>
   </si>
   <si>
-    <t>CORR BANK'S INT</t>
-  </si>
-  <si>
-    <t>UPAS Liabilitie</t>
-  </si>
-  <si>
-    <t>GRN</t>
-  </si>
-  <si>
-    <t>Long term Loan &amp; Short term Loan</t>
-  </si>
-  <si>
-    <t>FUNDS REMITTED</t>
-  </si>
-  <si>
-    <t>Payment</t>
-  </si>
-  <si>
-    <t>15303010001:27201020010</t>
-  </si>
-  <si>
-    <t>45101010013:41101096008</t>
+    <t>Accessories/Fabrics/Spare Pars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREDIT RPT CRG </t>
+  </si>
+  <si>
+    <t>COURIER CHARGES</t>
+  </si>
+  <si>
+    <t>PROCESSING FEE OF CASH INCENTIVE</t>
+  </si>
+  <si>
+    <t>BANK CERTIFICATE FROM</t>
+  </si>
+  <si>
+    <t>PAYMENT  BENEFICIARY PURBASHA INSPECTION COMPANY</t>
+  </si>
+  <si>
+    <t>CIB CHARGE REALIZATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGULAR VALUE CLEARING CHARGE </t>
+  </si>
+  <si>
+    <t>OUTWARD REMITTANCE</t>
+  </si>
+  <si>
+    <t>BANK STATEMENT FROM</t>
+  </si>
+  <si>
+    <t>EXCISE DUTY</t>
+  </si>
+  <si>
+    <t>BILL OF ENTRY EXTENSION CHARGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT CERTISSUANCE CHARGE </t>
+  </si>
+  <si>
+    <t>CASH INCENTIVE FILE PROCESSING FEE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,16 +229,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -162,16 +277,79 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -450,24 +628,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D164EB4A-F712-4130-BEBA-AF20C37CF082}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" customWidth="1"/>
-    <col min="4" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -479,12 +658,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
       </c>
       <c r="E2">
         <v>15303010001</v>
@@ -493,12 +675,15 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
       </c>
       <c r="E3">
         <v>15303010001</v>
@@ -507,12 +692,15 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
       </c>
       <c r="E4">
         <v>15303010001</v>
@@ -521,152 +709,334 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>15303010001</v>
-      </c>
-      <c r="F5">
-        <v>27201020010</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
         <v>45101010013</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6">
         <v>45101010013</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="F6">
+        <v>41101096008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>45101010013</v>
+      </c>
+      <c r="F7">
+        <v>41101096008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8">
         <v>45101010013</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D9">
         <v>45101010013</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10">
         <v>45101010013</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D11">
         <v>45101010013</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12">
-        <v>45101010013</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
+        <v>45101010014</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D13">
+        <v>45101010014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>45101010014</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>45101010014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <v>45101010004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="12">
         <v>15303010001</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14">
-        <v>45101010011</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
+      <c r="E26" s="13"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D26:E26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -675,16 +1045,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C535B3F7-9CCF-4C51-A335-606E16E1CF41}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" customWidth="1"/>
-    <col min="4" max="4" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -712,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>15303010001</v>
@@ -721,7 +1091,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -729,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>15303010001</v>
@@ -738,7 +1108,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -746,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>15303010001</v>
@@ -755,7 +1125,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -763,7 +1133,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>15303010001</v>
@@ -772,7 +1142,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -783,7 +1153,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>45101010013</v>
@@ -792,7 +1162,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -806,7 +1176,7 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -817,7 +1187,7 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>45101010013</v>
@@ -826,7 +1196,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -837,7 +1207,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9">
         <v>45101010013</v>
@@ -846,7 +1216,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -857,7 +1227,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E10">
         <v>45101010013</v>
@@ -866,7 +1236,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -877,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11">
         <v>45101010013</v>
@@ -886,7 +1256,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -900,32 +1270,32 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F13">
         <v>45101010011</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Cash_Management_Entry.xlsx
+++ b/Excel/Cash_Management_Entry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RPA\Desktop\AccountsPayableProd_Citi\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emon\Documents\UiPath\AccountsPayableProd\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33109286-C67F-4868-8E13-E8F358470096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12056502-949E-4B46-B9BA-63E51D916631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CITI" sheetId="2" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -136,9 +133,6 @@
     <t>ENDORSEMENT FEE</t>
   </si>
   <si>
-    <t>STAMP CHARGES COLLECTED</t>
-  </si>
-  <si>
     <t>NOC ISSUANCE CHARGE</t>
   </si>
   <si>
@@ -200,13 +194,16 @@
   </si>
   <si>
     <t>CASH INCENTIVE FILE PROCESSING FEE</t>
+  </si>
+  <si>
+    <t>STAMP CHARGE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,29 +235,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -324,21 +309,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -348,8 +331,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -628,17 +610,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D164EB4A-F712-4130-BEBA-AF20C37CF082}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" customWidth="1"/>
+    <col min="4" max="4" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -658,7 +640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -675,7 +657,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -692,7 +674,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -709,7 +691,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -723,8 +705,8 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -743,9 +725,9 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>35</v>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -763,9 +745,9 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>36</v>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
@@ -777,24 +759,24 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>45101010013</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>45101010013</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
@@ -805,9 +787,9 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>54</v>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
@@ -819,9 +801,9 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>38</v>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
@@ -833,9 +815,9 @@
         <v>45101010014</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>39</v>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>12</v>
@@ -847,9 +829,9 @@
         <v>45101010014</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>46</v>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -861,9 +843,9 @@
         <v>45101010014</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>56</v>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>12</v>
@@ -875,9 +857,9 @@
         <v>45101010014</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>51</v>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
@@ -889,9 +871,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>37</v>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
@@ -903,9 +885,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>47</v>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>12</v>
@@ -917,9 +899,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>48</v>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
@@ -931,9 +913,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>40</v>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
@@ -945,9 +927,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>49</v>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>12</v>
@@ -959,9 +941,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>55</v>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>12</v>
@@ -973,9 +955,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>50</v>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
@@ -987,9 +969,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>52</v>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
@@ -1001,9 +983,9 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>12</v>
@@ -1015,23 +997,20 @@
         <v>45101010004</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <v>15303010001</v>
       </c>
-      <c r="E26" s="13"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
+      <c r="E26" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1045,16 +1024,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C535B3F7-9CCF-4C51-A335-606E16E1CF41}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" customWidth="1"/>
+    <col min="4" max="4" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1091,7 +1070,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1108,7 +1087,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1125,7 +1104,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1142,7 +1121,7 @@
         <v>27201020010</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1162,7 +1141,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1176,7 +1155,7 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1196,7 +1175,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1216,7 +1195,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1236,7 +1215,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1256,7 +1235,7 @@
         <v>41101096008</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1270,7 +1249,7 @@
         <v>45101010013</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1290,7 +1269,7 @@
         <v>45101010011</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>

--- a/Excel/Cash_Management_Entry.xlsx
+++ b/Excel/Cash_Management_Entry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emon\Documents\UiPath\AccountsPayableProd\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12056502-949E-4B46-B9BA-63E51D916631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE92315F-64A0-43CD-A938-D355A7BAD9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,9 +154,6 @@
     <t>Prepayment</t>
   </si>
   <si>
-    <t>Accessories/Fabrics/Spare Pars</t>
-  </si>
-  <si>
     <t xml:space="preserve">CREDIT RPT CRG </t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>STAMP CHARGE</t>
+  </si>
+  <si>
+    <t>TT</t>
   </si>
 </sst>
 </file>
@@ -642,24 +642,21 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>15303010001</v>
-      </c>
-      <c r="F2">
-        <v>27201020010</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>45101010013</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
@@ -676,7 +673,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -693,16 +690,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>45101010013</v>
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>15303010001</v>
+      </c>
+      <c r="F5">
+        <v>27201020010</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -727,7 +727,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -845,7 +845,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>12</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>12</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>12</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>12</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>12</v>
@@ -1002,7 +1002,7 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>41</v>

--- a/Excel/Cash_Management_Entry.xlsx
+++ b/Excel/Cash_Management_Entry.xlsx
@@ -14,9 +14,15 @@
     <sheet name="EUR_Patterns" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="SCB_Rules" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Bank_Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CITI_Rules" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="HSBC_Rules" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DB_Rules" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SCB_Rules'!$A$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'CITI_Rules'!$A$1:$E$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'HSBC_Rules'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'DB_Rules'!$A$1:$E$72</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,6 +94,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -737,6 +744,4331 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Used_In</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bank_Code</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bank these rules belong to</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Event_Sheet</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sheet in Cash_Management_Entry.xlsx with the SCB event map (see Bank_Config)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Event_Key_Column</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>HSBC_Expense_Type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Column of the event sheet matched against the advice expense type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Output_Sheet</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The one output sheet written back to the statement file</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Evt_TT_Commission</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>COMMISSION- OTT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Evt_Interest</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CORR BANK'S INT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Evt_Remitted</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>FUNDS REMITTED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Evt_Import_Bill</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Evt_SG_Charge</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>S/G ISS CHARGES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SG_LC_Start</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>L/CNO:</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SG_LC_End</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Payment_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPE value that makes the row a PAYMENT action</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Account_Marker_GRN</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>GRN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Value of ACCOUNT in the event map that sends the row down the GRN path</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eur_Trigger_Currency</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Statement currency of a row that can be an EUR advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Foreign_Tag</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Foreign</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>First word of COUNTRY_ORIGIN for a foreign supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Foreign_Default_Type</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Prepayment</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TYPE when the event map has none and the supplier is foreign</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Local_Default_Type</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TYPE when the event map has none and the supplier is local</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Amount_End_Text</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>.0000000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tenor_Regex</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>TENOR(\d+)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR branch</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex_EurPair</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+EUR\s+([\d,]+\.\d+)\s+[\d.]+\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex_Single</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EUR_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+EUR\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Commission_Regex</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>COMMISSION- OTT\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TT_Account</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>15303010001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GL account for the TT amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUR_Account_Value</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / EUR branch</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Value written to EUR_Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asset_Account</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>11401010001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR / Machinery</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machinery asset GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Interest_Account</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>45101010012</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR / Machinery</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machinery interest GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Commission_Account</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>EVENT.ACCOUNT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not hardcoded: commission account is the ACCOUNT of the event map row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EUR_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / EUR branch</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Value written to EUR_Amount_Expense_Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPES</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TT_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Value written to TT_Amount_Expense_Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Int_Description_Find</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>CORR BANK'S INT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Int_Description_Replace</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>INT ON UPAS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Int_Invoice_Suffix</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>_INT_UPAS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for HSBC (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Description_Pattern</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>{EXPENSE}_LC-{LC}_{BATCH}_{SUPPLIER}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DESCRIPTION of a normal row. Tokens: {EXPENSE} event map expense type, {LC} LC number, {BATCH} unit / batch name, {SUPPLIER} beneficiary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TT_Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TT_INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TT_Description_Rule</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TT_DESCRIPTION rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Commission_Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>COMMISION_TT_INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Commission_Description_Rule</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>COMMISION_TT_DESCRIPTION rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Voucher_Columns</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Invoice_Voucher_No|Payment_Number|Clear_Transaction|EUR_VOUCHER_NUMBER|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Left empty here, filled after the real invoice is created</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Action_Normal</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_NORMAL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Invoice with no failure text</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Action_TT</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_TT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Row with a TT amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Action_GRN</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_GRN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GRN or EUR row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Action_Machinery</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_MACHINERY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machinery row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Action_Payment</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Payment row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Action_Ignore</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Row the robot must skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ignore_Report_Regex</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>not found|ignore|not searchable|not built|mail not|not in the \w+ map</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Report text (any case) that makes the row IGNORE. "no advice" is left out on purpose: a row with no advice still takes its type from the statement description</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Machinery_Country_Keywords</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>MACHINARY|MACHINERY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>COUNTRY_ORIGIN text (any case) that marks Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Machinery_From_Action</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_GRN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Only a row that would be this action becomes Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cols_EUR</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>EUR_Amount|EUR_Amount_Expense_Type|EUR_Account|EUR_VOUCHER_NUMBER</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Part 2 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cols_TT</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>TT_Amount|TT_Amount_Expense_Type|TT_Account|TT_INVOICE_NO|TT_DESCRIPTION|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT|COMMISION_TT_Expense_Type|COMMISION_TT_Acount|COMMISION_TT_INVOICE_NO|COMMISION_TT_DESCRIPTION|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Part 3 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cols_GRN</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>GRN_NUMBER|REMITTED_AMOUNT|INT_AMOUNT|Match_Invoice_No</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Part 4 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cols_Machinery</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Asset_Date|Loan_Date|Tenor_Days|Tenor_Date|Asset_Value|Interest_Value|Asset_Account|Interest_Account</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Part 5 columns, in output order (cleared on non-Machinery rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Color_Common</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>1F4E78</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 1 (common)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Color_EUR</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2E7D32</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Color_TT</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>C55A11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Color_GRN</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>7030A0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Color_Machinery</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>806000</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Trading_Partner</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>HSBC-BP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>bank advice reader</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TRADING_PARTNER written on every row of this bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Min_Key_Length</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>bank advice reader</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Shortest event-map key allowed when matching the statement description</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Adv_Invoice_Regex</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>(?:Open Account Amount|Documentary Credit Amount|Bill Amount|Goods Value|Invoice Amount|Drawing Amount)\s*:\s*([A-Z]{3})\s*([\d,]+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Invoice currency (group 1) and amount (group 2); same layout as EUR_Patterns</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Adv_Account_Regex</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>(\d{3}-\d{6}-\d{3})</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Account number printed on the advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Min_Ref_Length</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Shortest bank reference accepted when searching the PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Route_Invoice_Ccy_Routes</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>EUR|MACHINERY</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Event-map routes (Output_Sheet) that follow the invoice currency instead of the statement currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LC_Number_Regex</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>^(OAA|OAR|DC|DP)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Statement references that are real LC numbers (regex, any case). Blank = any non-empty LC_NUMBER. HSBC: OAA, OAR (OARBD...), DC, DP; NONREF and other references are not looked up</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TT amount on a TT advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TT_Commission_Regex</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TT commission on a TT advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GRN_Remitted_Regex</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Remitted amount on a GRN advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GRN_Interest_Regex</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Interest amount on a GRN advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Machinery_Loan_Date_Regex</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Loan date on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Machinery_Asset_Date_Regex</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Asset date on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Machinery_Tenor_Regex</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Tenor days on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Skip_Review_Text</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>NEEDS DECISION</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>An event-map row whose Review column contains this text is not processed: the row is reported as Ignore</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LC_Lookup_Suffix</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Added to LC_NUMBER before the BBLC / CMLC lookup. SCB LC numbers need -L; other banks use none</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Adv_Component_Regex</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>^(.+?)\s+[A-Z]{3}\s+([\d,]+\.\d{2})\s+DR\s*$</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Charge line of the advice: description (group 1) and amount (group 2); several lines can add up to the statement amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Adv_Total_Text</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Lines containing this text are totals and are not added up</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Advice_Required_Column</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Event-map column that says whether an advice is needed (Yes / No). Blank = Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LC_Required_Column</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Event-map column that says whether the LC lookup is needed (Must / No). Blank = LC lookup only when the advice is EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Adv_LC_Regex</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>(?:Documentary Credit No\.?|Our Reference No\.?)\s*:\s*([A-Za-z0-9\-]+)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>HSBC_advice_reader</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LC number printed on the advice (group 1); labels differ between advice types - add a label to the list with | when a new one appears. The first number that looks like an LC (LC_Number_Regex) is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mail_Days_Before</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Days before the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Mail_Days_After</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Days after the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E73"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Used_In</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bank_Code</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bank these rules belong to</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Event_Sheet</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sheet in Cash_Management_Entry.xlsx with the SCB event map (see Bank_Config)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Event_Key_Column</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>DB_Expense_Type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Column of the event sheet matched against the advice expense type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Output_Sheet</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The one output sheet written back to the statement file</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Evt_TT_Commission</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>COMMISSION- OTT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Evt_Interest</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CORR BANK'S INT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Evt_Remitted</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>FUNDS REMITTED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Evt_Import_Bill</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Evt_SG_Charge</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>S/G ISS CHARGES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SG_LC_Start</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>L/CNO:</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SG_LC_End</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Payment_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPE value that makes the row a PAYMENT action</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Account_Marker_GRN</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>GRN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Value of ACCOUNT in the event map that sends the row down the GRN path</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eur_Trigger_Currency</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Statement currency of a row that can be an EUR advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Foreign_Tag</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Foreign</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>First word of COUNTRY_ORIGIN for a foreign supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Foreign_Default_Type</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Prepayment</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TYPE when the event map has none and the supplier is foreign</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Local_Default_Type</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TYPE when the event map has none and the supplier is local</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Amount_End_Text</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>.0000000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tenor_Regex</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>TENOR(\d+)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR branch</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex_EurPair</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+EUR\s+([\d,]+\.\d+)\s+[\d.]+\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex_Single</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EUR_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+EUR\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Commission_Regex</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>COMMISSION- OTT\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TT_Account</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>15303010001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GL account for the TT amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUR_Account_Value</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / EUR branch</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Value written to EUR_Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asset_Account</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>11401010001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR / Machinery</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machinery asset GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Interest_Account</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>45101010012</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR / Machinery</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machinery interest GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Commission_Account</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>EVENT.ACCOUNT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not hardcoded: commission account is the ACCOUNT of the event map row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EUR_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / EUR branch</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Value written to EUR_Amount_Expense_Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPES</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TT_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Value written to TT_Amount_Expense_Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Int_Description_Find</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>CORR BANK'S INT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Int_Description_Replace</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>INT ON UPAS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Int_Invoice_Suffix</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>_INT_UPAS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for DB (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Description_Pattern</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>{EXPENSE}_LC-{LC}_{BATCH}_{SUPPLIER}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DESCRIPTION of a normal row. Tokens: {EXPENSE} event map expense type, {LC} LC number, {BATCH} unit / batch name, {SUPPLIER} beneficiary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TT_Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TT_INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TT_Description_Rule</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TT_DESCRIPTION rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Commission_Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>COMMISION_TT_INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Commission_Description_Rule</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>COMMISION_TT_DESCRIPTION rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Voucher_Columns</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Invoice_Voucher_No|Payment_Number|Clear_Transaction|EUR_VOUCHER_NUMBER|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Left empty here, filled after the real invoice is created</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Action_Normal</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_NORMAL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Invoice with no failure text</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Action_TT</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_TT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Row with a TT amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Action_GRN</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_GRN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GRN or EUR row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Action_Machinery</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_MACHINERY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machinery row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Action_Payment</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Payment row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Action_Ignore</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Row the robot must skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ignore_Report_Regex</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>not found|ignore|not searchable|not built|mail not|not in the \w+ map</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Report text (any case) that makes the row IGNORE. "no advice" is left out on purpose: a row with no advice still takes its type from the statement description</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Machinery_Country_Keywords</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>MACHINARY|MACHINERY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>COUNTRY_ORIGIN text (any case) that marks Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Machinery_From_Action</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_GRN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Only a row that would be this action becomes Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cols_EUR</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>EUR_Amount|EUR_Amount_Expense_Type|EUR_Account|EUR_VOUCHER_NUMBER</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Part 2 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cols_TT</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>TT_Amount|TT_Amount_Expense_Type|TT_Account|TT_INVOICE_NO|TT_DESCRIPTION|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT|COMMISION_TT_Expense_Type|COMMISION_TT_Acount|COMMISION_TT_INVOICE_NO|COMMISION_TT_DESCRIPTION|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Part 3 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cols_GRN</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>GRN_NUMBER|REMITTED_AMOUNT|INT_AMOUNT|Match_Invoice_No</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Part 4 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cols_Machinery</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Asset_Date|Loan_Date|Tenor_Days|Tenor_Date|Asset_Value|Interest_Value|Asset_Account|Interest_Account</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Part 5 columns, in output order (cleared on non-Machinery rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Color_Common</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>1F4E78</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 1 (common)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Color_EUR</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2E7D32</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Color_TT</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>C55A11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Color_GRN</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>7030A0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Color_Machinery</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>806000</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Trading_Partner</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Dhaka Bank Ltd-BP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>bank advice reader</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TRADING_PARTNER written on every row of this bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Min_Key_Length</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>bank advice reader</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Shortest event-map key allowed when matching the statement description</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Adv_Debit_Line_Regex</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>^[ \t]*(.+?)[ \t]+D[ \t]+([A-Z]{3})[ \t]+([\d,]+\.\d{2})[ \t]+([A-Z0-9]{8,})[ \t\r]*$</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DB_advice_reader</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Debit line: type, currency, amount, account</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Adv_Title_Regex</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>(?m)^[ \t]*([A-Z/ ]*ADVICE[A-Z/ ]*)[ \t\r]*$</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DB_advice_reader</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Advice title</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Adv_Contract_Regex</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>\b225[A-Z]{2,6}\d{6,}\b</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DB_advice_reader</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Contract number. Starts with 225 (year code) - change it when the year code changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LC_Number_Regex</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Statement references that are real LC numbers (regex, any case). Blank = any non-empty LC_NUMBER. HSBC: OAA, OAR (OARBD...), DC, DP; NONREF and other references are not looked up</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TT amount on a TT advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TT_Commission_Regex</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TT commission on a TT advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GRN_Remitted_Regex</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Remitted amount on a GRN advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GRN_Interest_Regex</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Interest amount on a GRN advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Machinery_Loan_Date_Regex</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Loan date on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Machinery_Asset_Date_Regex</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Asset date on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Machinery_Tenor_Regex</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Tenor days on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LC_Lookup_Suffix</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Added to LC_NUMBER before the BBLC / CMLC lookup. SCB LC numbers need -L; other banks use none</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Advice_Required_Column</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Event-map column that says whether an advice is needed (Yes / No). Blank = Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LC_Required_Column</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Event-map column that says whether the LC lookup is needed (Must / No). Blank = LC lookup only when the advice is EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Mail_Days_Before</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Days before the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mail_Days_After</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Days after the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E72"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1542,8 +5874,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1591,6 +5928,21 @@
           <t>Output_Sheet</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Account_Section</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1623,6 +5975,21 @@
           <t>IMPORT DC ISSUANCE|DC ISSUE COMM CHARGES|LC ISSUING COMM</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1650,6 +6017,21 @@
           <t>27201020010</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1682,6 +6064,21 @@
           <t>IMPORT DC BILL ACCEPTANCE|IMPORT DC PAID|ACCEPTANCE COMM</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1714,6 +6111,21 @@
           <t>IMPORT DC AMENDMENT|DC AMENDMENT COMM CHARGES|IMP BILL AMEND. CHARGES</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1751,6 +6163,21 @@
           <t>TT@USD|TT@EUR</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CD|ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1783,6 +6210,21 @@
           <t>manual sheets use 45101010013 (and 45101010004 in some months)</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1810,6 +6252,21 @@
           <t>CREDIT REPORT</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1847,6 +6304,21 @@
           <t>BUY ACTIVITY</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1879,6 +6351,21 @@
           <t>41101096008</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1916,6 +6403,21 @@
           <t>STAMP CHARGE</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1953,6 +6455,21 @@
           <t>HANDLING FEES|CASH INCENTIV HANDLING</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1990,6 +6507,21 @@
           <t>IMP SHIPPG GTEE|CARGO RELEASE ISSUANCE|SHIPPING GU</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2027,6 +6559,21 @@
           <t>REIMBURSEMENT</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2086,6 +6633,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2108,6 +6670,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2135,6 +6712,21 @@
           <t>EXCISE DUTY</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BDT=No|USD=Yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CD|ERQ|MOB</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2157,6 +6749,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2184,6 +6791,21 @@
           <t>ACC MAINT|ACCOUNT MAINT|MAINTENANCE FEE|A/C MAINT</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2206,6 +6828,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2233,6 +6870,21 @@
           <t>PROFESSIONAL FEES|INSPECTION</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2255,6 +6907,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2277,6 +6944,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2299,6 +6981,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2321,6 +7018,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2343,6 +7055,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2370,6 +7097,21 @@
           <t>COMMSN AGNST RTGS|AGAI NST RTGS|AGAINST RTGS TXN</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2397,6 +7139,21 @@
           <t>ACC MAINT FEE</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2419,6 +7176,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2451,6 +7223,21 @@
           <t>export</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2483,6 +7270,21 @@
           <t>export</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2515,6 +7317,21 @@
           <t>export</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2537,6 +7354,21 @@
           <t>45101010014</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2564,6 +7396,21 @@
           <t>DEBIT INTEREST|INTEREST ON OD</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2586,6 +7433,21 @@
           <t>45101010002</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2608,6 +7470,21 @@
           <t>45101010001</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2630,6 +7507,21 @@
           <t>27401010002</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2652,6 +7544,21 @@
           <t>24201010001</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2674,6 +7581,21 @@
           <t>27401010002</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2696,6 +7618,21 @@
           <t>24201010001</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2745,6 +7682,21 @@
           <t>export</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2782,6 +7734,21 @@
           <t>TT@USD|TT@EUR</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2819,6 +7786,21 @@
           <t>MACHINERY@EUR|GRN@USD</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>MOB</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2917,6 +7899,21 @@
           <t>seen in manual sheets (local/foreign); no unique statement wording</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2944,6 +7941,21 @@
           <t>IMPORT DOC EXAM</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2971,6 +7983,21 @@
           <t>FREIGHT CERT</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2998,6 +8025,21 @@
           <t>B2B CERTIFICATE|CERT ISSUE</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3030,6 +8072,21 @@
           <t>manual sheets mark these BC IMPORT; account inferred as 45101010004</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>BDT=No|USD=Yes</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>CD|ERQ|MOB</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3057,6 +8114,21 @@
           <t>FEE AGAINST 01 FCY RTGS|FEE AGAINST FCY RTGS|FEE FOR FCY RTGS|FEE AGNST|FEE AGSNT</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3084,6 +8156,21 @@
           <t>VAT ON FCY RTGS|VAT AGAINST 01 FCY RTGS|VAT FOR CHARGES OF RTGS|VAT ON RTGS|VAT 15% AGAINST ORM</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3111,6 +8198,21 @@
           <t>H2H MONTHLY</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3138,6 +8240,21 @@
           <t>HSBCNET FEES|HSBC NET FEES|HSBCNET VAT</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3165,6 +8282,21 @@
           <t>CLG CHQ CHARGE</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3192,6 +8324,21 @@
           <t>CIB FEES|CIB ONLINE</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3278,6 +8425,21 @@
           <t>export; account inferred like other export charges</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3310,6 +8472,21 @@
           <t>export; account inferred like other export charges</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3393,6 +8570,21 @@
           <t>NEEDS DECISION: rule file says Need to Discuss</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3542,7 +8734,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MATURITY BILL PAYMENT/COMM|MATURITY BILL PAYMENT/TELE</t>
+          <t>IMP BILL RETIRE. CHARGES</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
@@ -3620,12 +8827,27 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ADVANCE PAYMENT FOR|PRICEWATERHOUSE|REPRESENTATIVE OFFICE</t>
+          <t>ADVANCE PAYMENT FOR|PRICEWATERHOUSE|REPRESENTATIVE OFFICE|OT ERQ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>NEEDS DECISION: rule file says Need to Discuss (service TT payment)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>ERQ</t>
         </is>
       </c>
     </row>
@@ -3690,6 +8912,58 @@
       <c r="I79" t="inlineStr">
         <is>
           <t>MACHINERY@EUR|GRN@USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Import OA Principal (ERQ)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Accessories/Fabrics/Spare Pars</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Prepayment</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>15303010001</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>IMP OA RECORDING/OCMT</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ERQ USD principal of an import open-account bill (manual sheets); pairs with Remitting Bank Charges (IMP OA RECORDING/CHRG on the BDT account). TT amount comes from the advice</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TT@USD|TT@EUR</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>ERQ</t>
         </is>
       </c>
     </row>
@@ -5365,7 +10639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6965,6 +12239,218 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>Hex RRGGBB, part 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Trading_Partner</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank-BP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SCB uses the Trading_Partner argument of Advice_pdf (same value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LC_Lookup_Suffix</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>-L</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Added to LC_NUMBER before the BBLC / CMLC lookup. SCB LC numbers need -L; other banks use none</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Advice_Required_Column</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Not used for SCB (no event-map flags); present so the shared step never lacks the key</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LC_Required_Column</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Not used for SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Min_Key_Length</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Not used for SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LC_Number_Regex</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Statement references that are real LC numbers (regex, any case). Blank = any non-empty LC_NUMBER. HSBC: OAA, OAR (OARBD...), DC, DP; NONREF and other references are not looked up</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mail_Days_Before</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Days before the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mail_Days_After</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Days after the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
         </is>
       </c>
     </row>
@@ -7071,7 +12557,11 @@
           <t>CITI_Expense_Type</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CITI_Rules</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>CITI.xlsx</t>
@@ -7079,7 +12569,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Event map ready; rules sheet not made yet</t>
+          <t>Rules sheet ready (advice layout keys); TT / GRN / Machinery advice rules are TBD</t>
         </is>
       </c>
     </row>
@@ -7099,7 +12589,11 @@
           <t>HSBC_Expense_Type</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HSBC_Rules</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>HSBC.xlsx</t>
@@ -7107,7 +12601,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Event map ready; rules sheet not made yet</t>
+          <t>Rules sheet ready (advice layout keys); TT / GRN / Machinery advice rules are TBD</t>
         </is>
       </c>
     </row>
@@ -7127,7 +12621,11 @@
           <t>DB_Expense_Type</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DB_Rules</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>DHAKABANK.xlsx</t>
@@ -7135,11 +12633,2239 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Event map ready; rules sheet not made yet</t>
+          <t>Rules sheet ready (advice layout keys); TT / GRN / Machinery advice rules are TBD</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Used_In</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bank_Code</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>CITI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bank these rules belong to</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Event_Sheet</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CITI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sheet in Cash_Management_Entry.xlsx with the SCB event map (see Bank_Config)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Event_Key_Column</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>CITI_Expense_Type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Column of the event sheet matched against the advice expense type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Output_Sheet</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The one output sheet written back to the statement file</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Evt_TT_Commission</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>COMMISSION- OTT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Evt_Interest</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CORR BANK'S INT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Evt_Remitted</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>FUNDS REMITTED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Evt_Import_Bill</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Evt_SG_Charge</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>S/G ISS CHARGES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SG_LC_Start</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>L/CNO:</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SG_LC_End</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Payment_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPE value that makes the row a PAYMENT action</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Account_Marker_GRN</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>GRN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Value of ACCOUNT in the event map that sends the row down the GRN path</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eur_Trigger_Currency</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Statement currency of a row that can be an EUR advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Foreign_Tag</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Foreign</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>First word of COUNTRY_ORIGIN for a foreign supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Foreign_Default_Type</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Prepayment</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TYPE when the event map has none and the supplier is foreign</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Local_Default_Type</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TYPE when the event map has none and the supplier is local</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Amount_End_Text</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>.0000000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tenor_Regex</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>TENOR(\d+)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR branch</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex_EurPair</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+EUR\s+([\d,]+\.\d+)\s+[\d.]+\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex_Single</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EUR_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL\s+EUR\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Commission_Regex</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>COMMISSION- OTT\s+[A-Z]{3}\s+([\d,]+\.\d+)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TT_Account</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>15303010001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GL account for the TT amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUR_Account_Value</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / EUR branch</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Value written to EUR_Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asset_Account</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>11401010001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR / Machinery</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machinery asset GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Interest_Account</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>45101010012</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Advice_pdf EUR / Machinery</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machinery interest GL account</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Commission_Account</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>EVENT.ACCOUNT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not hardcoded: commission account is the ACCOUNT of the event map row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EUR_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT / EUR branch</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Value written to EUR_Amount_Expense_Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXPENSE_TYPES</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TT_Expense_Type</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT OF IMPORT BILL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Advice_pdf TT branch</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Value written to TT_Amount_Expense_Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Int_Description_Find</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>CORR BANK'S INT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Int_Description_Replace</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>INT ON UPAS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GRN_INTEREST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Int_Invoice_Suffix</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>_INT_UPAS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Advice_pdf GRN / EUR branch</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SCB advice layout - not used for CITI (own value: see the Adv_* rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Description_Pattern</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>{EXPENSE}_LC-{LC}_{BATCH}_{SUPPLIER}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DESCRIPTION of a normal row. Tokens: {EXPENSE} event map expense type, {LC} LC number, {BATCH} unit / batch name, {SUPPLIER} beneficiary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TT_Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TT_INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TT_Description_Rule</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TT_DESCRIPTION rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Commission_Invoice_No_Rule</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>COMMISION_TT_INVOICE_NO rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Commission_Description_Rule</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>COMMISION_TT_DESCRIPTION rule - to be provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>INVOICE_RULES</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Voucher_Columns</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Invoice_Voucher_No|Payment_Number|Clear_Transaction|EUR_VOUCHER_NUMBER|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Left empty here, filled after the real invoice is created</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Action_Normal</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_NORMAL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Invoice with no failure text</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Action_TT</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_TT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Row with a TT amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Action_GRN</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_GRN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GRN or EUR row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Action_Machinery</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_MACHINERY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machinery row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Action_Payment</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Payment row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Action_Ignore</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Row the robot must skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ignore_Report_Regex</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>not found|ignore|not searchable|not built|mail not|not in the \w+ map</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Report text (any case) that makes the row IGNORE. "no advice" is left out on purpose: a row with no advice still takes its type from the statement description</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Machinery_Country_Keywords</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>MACHINARY|MACHINERY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>COUNTRY_ORIGIN text (any case) that marks Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ACTIONS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Machinery_From_Action</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>INVOICE_GRN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Advice_pdf final table</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Only a row that would be this action becomes Machinery</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cols_EUR</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>EUR_Amount|EUR_Amount_Expense_Type|EUR_Account|EUR_VOUCHER_NUMBER</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Part 2 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cols_TT</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>TT_Amount|TT_Amount_Expense_Type|TT_Account|TT_INVOICE_NO|TT_DESCRIPTION|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT|COMMISION_TT_Expense_Type|COMMISION_TT_Acount|COMMISION_TT_INVOICE_NO|COMMISION_TT_DESCRIPTION|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Part 3 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cols_GRN</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>GRN_NUMBER|REMITTED_AMOUNT|INT_AMOUNT|Match_Invoice_No</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Part 4 columns, in output order</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cols_Machinery</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Asset_Date|Loan_Date|Tenor_Days|Tenor_Date|Asset_Value|Interest_Value|Asset_Account|Interest_Account</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Part 5 columns, in output order (cleared on non-Machinery rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Color_Common</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>1F4E78</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 1 (common)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Color_EUR</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2E7D32</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Color_TT</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>C55A11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Color_GRN</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>7030A0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Color_Machinery</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>806000</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Advice_pdf header colour</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Hex RRGGBB, part 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Trading_Partner</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Citibank, N.A.-BP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>bank advice reader</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TRADING_PARTNER written on every row of this bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Min_Key_Length</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>bank advice reader</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Shortest event-map key allowed when matching the statement description</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Adv_Total_Debited_Regex</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT DEBITED:\s*[A-Z]{3}\s*([\d,]+\.?\d*)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Total debited on the advice (group 1); compared with the statement amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Adv_Total_Debited_Text_Regex</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT DEBITED:\s*([A-Z]{3}\s*[\d,\.]+)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Same, with the currency, for the Report text</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Adv_Your_Ref_Regex</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>YOUR REF\s*:\s*([^\r\n]+)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>YOUR REF line -&gt; BANK_DC_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Adv_Account_Regex</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>ACCOUNT NO\.\s*(\d+)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Debited account number</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Adv_Beneficiary_Regex</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>BENEFECIARY\s*:\s*([^\r\n]+)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Beneficiary line (spelling as printed on the advice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Adv_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>(?:LC|BILL) AMOUNT\s*:\s*([A-Z]{3}\s*[\d,\.]+)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LC or bill amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Adv_Representing_Regex</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>REPRESENTING:\s*[\r\n]+\s*([^\r\n]+)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Line after REPRESENTING: = the charge type</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Adv_Line_Map</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>LC ISSUANCE COMMISSION=&gt;LC ISSUANCE COMMISSION|LC AMENDMENT COMMISSION=&gt;LC AMENDMENT COMMISSION|ACCEPTANCE COMMISSION=&gt;ACCEPTANCE COMMISSION CHARGE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>REPRESENTING line starts with (left) -&gt; event-map key (right); pairs separated by |</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LC_Number_Regex</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Statement references that are real LC numbers (regex, any case). Blank = any non-empty LC_NUMBER. HSBC: OAA, OAR (OARBD...), DC, DP; NONREF and other references are not looked up</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TT_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TT amount on a TT advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TT_Commission_Regex</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TT commission on a TT advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GRN_Remitted_Regex</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Remitted amount on a GRN advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GRN_Interest_Regex</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Interest amount on a GRN advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Machinery_Loan_Date_Regex</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Loan date on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Machinery_Asset_Date_Regex</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Asset date on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Machinery_Tenor_Regex</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Tenor days on a Machinery advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LC_Lookup_Suffix</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Added to LC_NUMBER before the BBLC / CMLC lookup. SCB LC numbers need -L; other banks use none</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Advice_Required_Column</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Event-map column that says whether an advice is needed (Yes / No). Blank = Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LC_Required_Column</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Event-map column that says whether the LC lookup is needed (Must / No). Blank = LC lookup only when the advice is EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mail_Days_Before</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Days before the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Mail_Days_After</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>outlook_mailbox</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Days after the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E77"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Excel/Cash_Management_Entry.xlsx
+++ b/Excel/Cash_Management_Entry.xlsx
@@ -17,6 +17,7 @@
     <sheet name="CITI_Rules" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="HSBC_Rules" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="DB_Rules" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CITI_Units" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SCB_Rules'!$A$1:$E$59</definedName>
@@ -2982,7 +2983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4731,15 +4732,19 @@
           <t>LC_Number_Regex</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n"/>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>^(1418\d{8,9}|\d{3}CTCF\d{9})$</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>later</t>
+          <t>Advice_pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Statement references that are real LC numbers (regex, any case). Blank = any non-empty LC_NUMBER. HSBC: OAA, OAR (OARBD...), DC, DP; NONREF and other references are not looked up</t>
+          <t>Real Dhaka Bank LC number: 1418 + 8 or 9 digits (12 or 13 digits, no B01/G01 suffix, no dot), or the CTCF form such as 202CTCF170730026</t>
         </is>
       </c>
     </row>
@@ -5063,8 +5068,275 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LC_Statement_Regex</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>(?&lt;![A-Za-z0-9])(1418\d{8,9}|\d{3}CTCF\d{9})(?:[BG]\d{2})?(?![A-Za-z0-9])</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Bank_Statement</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LC number found anywhere in the statement description (group 1 = the LC). An optional B01/B02 (import bill) or G01/G02 (shipping guarantee) suffix and a trailing dot are not part of it. When a suffix exists the full reference goes to BANK_DC_NO and is used to match the advice (OUR REF NO / USER REF NO)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E72"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Account_Number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>200153006</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>200153014</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>1200153029</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CGL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>200386019</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CGL</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>200386027</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CGL</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1200386015</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GFL</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>200837002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GFL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>200837029</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GFL</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1200837009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CWPL</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>200897005</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CWPL</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>200897013</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CWPL</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>200897021</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CITI statement account number -&gt; unit initials written to BATCH_NAME (Bank_Statement CITI branch); an LC lookup can overwrite it</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5075,7 +5347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.6328125" customWidth="1" min="1" max="1"/>
@@ -5131,6 +5403,21 @@
           <t>Output_Sheet</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Account_Section</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5154,6 +5441,21 @@
       <c r="F2" t="n">
         <v>27201020010</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5177,6 +5479,21 @@
       <c r="F3" t="n">
         <v>27201020010</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5200,6 +5517,21 @@
       <c r="F4" t="n">
         <v>27201020010</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5220,6 +5552,21 @@
       <c r="D5" t="n">
         <v>45101010013</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5248,6 +5595,21 @@
       <c r="F6" t="n">
         <v>41101096008</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5276,6 +5638,21 @@
       <c r="F7" t="n">
         <v>41101096008</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5296,6 +5673,21 @@
       <c r="D8" t="n">
         <v>45101010013</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5316,6 +5708,21 @@
       <c r="D9" t="n">
         <v>45101010013</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5336,6 +5743,21 @@
       <c r="D10" t="n">
         <v>45101010013</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5356,6 +5778,21 @@
       <c r="D11" t="n">
         <v>45101010013</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5376,6 +5813,21 @@
       <c r="D12" t="n">
         <v>45101010014</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5396,6 +5848,21 @@
       <c r="D13" t="n">
         <v>45101010014</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5416,6 +5883,21 @@
       <c r="D14" t="n">
         <v>45101010014</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5476,6 +5958,21 @@
       <c r="D17" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5496,6 +5993,21 @@
       <c r="D18" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5516,6 +6028,21 @@
       <c r="D19" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5536,6 +6063,21 @@
       <c r="D20" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5556,6 +6098,21 @@
       <c r="D21" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5576,6 +6133,21 @@
       <c r="D22" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5596,6 +6168,21 @@
       <c r="D23" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5636,6 +6223,21 @@
       <c r="D25" t="n">
         <v>45101010004</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>BDT=No|USD=Yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>BDT=No|USD=Must</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CD|ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5658,7 +6260,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TT@USD|TT@EUR</t>
+          <t>EUR@EUR|GRN@USD</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ERQ</t>
         </is>
       </c>
     </row>
@@ -5737,6 +6354,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5759,6 +6391,21 @@
           <t>45101010004</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5781,6 +6428,21 @@
           <t>45101010005</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5818,6 +6480,21 @@
           <t>MACHINERY@EUR|GRN@USD</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ERQ</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5860,6 +6537,356 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>MACHINERY@EUR|GRN@USD</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SUNDRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Interest ON STL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Short Term Loan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>45101010002</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STL Payment</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Short Term Loan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>27401010002</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Interest ON LTL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Long Term Loan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>45101010001</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LTL Payment</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Long Term Loan</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>24201010001</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STL Received</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Short Term Loan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Debit Memo</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>27401010002</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LTL Received</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Long Term Loan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>24201010001</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ORM TAX (WITHHOLDING)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>WITHOLDING TAX</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NEEDS DECISION: Citi NA: Need to Discuss - tax on foreign salary / service payment</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CD|ERQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OUTGOING RTGS TRANSFER (SALARY)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>OUTGOING RTGS TRANSFER</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NEEDS DECISION: Citi NA: Need to Discuss - salary / inland payment</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CD|ERQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FT OUTGOING - SWIFT</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>FT OUTGOING - SWIFT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NEEDS DECISION: Citi NA: Need to Discuss - foreign payment</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CD|ERQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UPAS Liabilitiy</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UPAS Liabilitie</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NEEDS DECISION: Citi NA says not automated - knock to bank then forward MS Excel advice; only payment invoice already prepared</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>SUNDRY</t>
         </is>
       </c>
     </row>
@@ -9370,7 +10397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9419,6 +10446,21 @@
           <t>Output_Sheet</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Advice_Required</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>LC_Required</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Account_Section</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9446,6 +10488,21 @@
           <t>27201020010</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9473,6 +10530,21 @@
           <t>27201020010</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9500,6 +10572,21 @@
           <t>27201020010</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9527,11 +10614,26 @@
           <t>27201020010</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APPLICATION CHARGE AGAINST</t>
+          <t>COURIER CHARGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9547,13 +10649,28 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TT CHG AGAINST FUND</t>
+          <t>Shipping guarantee issuance charge</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9569,13 +10686,28 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWIFT CHG AGAINST FUND</t>
+          <t>Certificate charge</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9591,13 +10723,28 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COURIER CHARGE</t>
+          <t>Credit Report Charge</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9613,13 +10760,28 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shipping guarantee issuance charge</t>
+          <t>IMPORT BILL RETIREMENT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9634,14 +10796,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>45101010013:41101096008</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>45101010013</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>41101096008</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Certificate charge</t>
+          <t>SG ISSUANCE CHARGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9656,19 +10843,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>45101010013:41101096008</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>45101010013</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>41101096008</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Credit Report Charge</t>
+          <t>LC STAMP CHARGE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
+          <t>LC OPENING CHAR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9678,19 +10890,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45101010013</t>
+          <t>15303010001:27201020010</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>15303010001</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>27201020010</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IMPORT BILL RETIREMENT</t>
+          <t>LC ISSUE SWIFT CHG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
+          <t>LC OPENING CHAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9700,29 +10937,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45101010013:41101096008</t>
+          <t>15303010001:27201020010</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45101010013</t>
+          <t>15303010001</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41101096008</t>
+          <t>27201020010</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SG ISSUANCE CHARGE</t>
+          <t>LC AMND SWIFT CHG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
+          <t>LC OPENING CHAR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9732,24 +10984,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45101010013:41101096008</t>
+          <t>15303010001:27201020010</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45101010013</t>
+          <t>15303010001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41101096008</t>
+          <t>27201020010</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LC STAMP CHARGE</t>
+          <t>CHARGE FOR CNF CERTIFICATE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9764,24 +11031,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45101010013:41101096008</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>45101010013</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>41101096008</t>
+          <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LC ISSUE SWIFT CHG</t>
+          <t>CHARGE FOR NOC CERTIFICATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9796,24 +11068,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45101010013:41101096008</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>45101010013</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>41101096008</t>
+          <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LC AMND SWIFT CHG</t>
+          <t>CHARGE FOR FOC CERTIFICATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9828,24 +11105,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45101010013:41101096008</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>45101010013</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>41101096008</t>
+          <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHARGE FOR CNF CERTIFICATE</t>
+          <t>CHARGE FOR BL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9861,13 +11143,28 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHARGE FOR NOC CERTIFICATE</t>
+          <t>CHARGES FOR BL ENDORSE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9883,13 +11180,28 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHARGE FOR FOC CERTIFICATE</t>
+          <t>PROCESSING FEE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9905,13 +11217,28 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHARGE FOR BL</t>
+          <t>EXCISE DUTY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9927,13 +11254,28 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHARGES FOR BL ENDORSE</t>
+          <t>BANKERS CHEQUE ISSUANCE COMMISSION</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9949,13 +11291,28 @@
       <c r="D22" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PROCESSING FEE</t>
+          <t>VAT on BANKERS CHEQUE ISSUANCE COMMISSION</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9971,13 +11328,28 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EXCISE DUTY</t>
+          <t>RJSC Search Report</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9993,13 +11365,28 @@
       <c r="D24" t="inlineStr">
         <is>
           <t>45101010004</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BANKERS CHEQUE ISSUANCE COMMISSION</t>
+          <t>BG DBLBG20262250400 BG  CASH COLLATERAL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10007,21 +11394,31 @@
           <t>OTHER CHARGES</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45101010004</t>
+          <t>15302020004</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VAT on BANKERS CHEQUE ISSUANCE COMMISSION</t>
+          <t>BG DBLBG20262250400 STAMP CHARGE REALIZE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10029,21 +11426,31 @@
           <t>OTHER CHARGES</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45101010004</t>
+          <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RJSC Search Report</t>
+          <t>BG DBLBG20262250400 ISSUE COMMISSION</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10051,21 +11458,31 @@
           <t>OTHER CHARGES</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45101010004</t>
+          <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BG DBLBG20262250400 BG  CASH COLLATERAL</t>
+          <t>BG DBLBG20262250400 VAT - BG COMMISION.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10075,14 +11492,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15302020004</t>
+          <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BG DBLBG20262250400 STAMP CHARGE REALIZE</t>
+          <t>BG Refund DBLBG20252252086 BG CASH COLLATERAL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10092,14 +11524,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45101010013</t>
+          <t>15302020004</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BG DBLBG20262250400 ISSUE COMMISSION</t>
+          <t>EXP CERTIFICATION</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10109,14 +11556,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45101010013</t>
+          <t>45101010014</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BG DBLBG20262250400 VAT - BG COMMISION.</t>
+          <t>MISCELLANEOUS CHARGE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -10126,14 +11588,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45101010013</t>
+          <t>45101010014</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BG Refund DBLBG20252252086 BG CASH COLLATERAL</t>
+          <t>EB COLLECTION CHARGE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -10143,31 +11620,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15302020004</t>
+          <t>45101010014</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EXP CERTIFICATION</t>
+          <t>IMPORT BILL LIQUIDATION</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>45101010014</t>
+          <t>Bills Payable</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DFC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MISCELLANEOUS CHARGE</t>
+          <t>FDD CHARGE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10175,16 +11667,36 @@
           <t>OTHER CHARGES</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>45101010014</t>
+          <t>45101010013</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DFC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EB COLLECTION CHARGE</t>
+          <t>TT ISSUE COMMISSION</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10192,21 +11704,46 @@
           <t>OTHER CHARGES</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>45101010014</t>
+          <t>45101010013</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TT@USD|TT@EUR</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Interrest on OD</t>
+          <t>Interest on EDF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
+          <t>EDF Liabilities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10216,19 +11753,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>45101010005</t>
+          <t>45101010010</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>MACHINERY@EUR|GRN@USD</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>DFC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Interest ON STL</t>
+          <t>DEBIT INTEREST</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Short Term Loan</t>
+          <t>OTHER CHARGES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10238,283 +11795,140 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>45101010002</t>
+          <t>45101010005</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Interest ON LTL</t>
+          <t>corresponding bank charge</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Long Term Loan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>45101010001</t>
+          <t>OTHER CHARGES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ERQ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STL Payment</t>
+          <t>EDF Liabilities</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Short Term Loan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>27401010002</t>
+          <t>EDF Liabilities</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>DFC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LTL Payment</t>
+          <t>Commission, SWIFT TT [Service]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Long Term Loan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>24201010001</t>
+          <t>OTHER CHARGES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STL Received</t>
+          <t>TT Goods related</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Short Term Loan</t>
+          <t>Accessories/Fabrics/Spare Pars</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Debit Memo</t>
+          <t>Prepayment</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27401010002</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LTL Received</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Long Term Loan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Debit Memo</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>24201010001</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>IMPORT BILL LIQUIDATION</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Bills Payable</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>FDD CHARGE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Bills Payable</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>45101010013</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TT ISSUE COMMISSION</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>OTHER CHARGES</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>45101010013</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
+          <t>15303010001</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>OUTWARD PAY|TT GOODS</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>TT@USD|TT@EUR</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Interest on EDF</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>EDF Liabilities</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>45101010010</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>MACHINERY@EUR|GRN@USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DEBIT INTEREST</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>OTHER CHARGES</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>45101010005</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>corresponding bank charge</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>OTHER CHARGES</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>EDF Liabilities</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EDF Liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>OUTWARD PAYMNET</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Accessories/Fabrics/Spare Pars</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Prepayment</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>15303010001</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>OUTWARD PAY|TT GOODS</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>TT@USD|TT@EUR</t>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ERQ</t>
         </is>
       </c>
     </row>
@@ -12569,7 +13983,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rules sheet ready (advice layout keys); TT / GRN / Machinery advice rules are TBD</t>
+          <t>Rules sheet ready; unit accounts in CITI_Units; routing PRINCIPAL -&gt; TT or Machinery (EUR bill also fills EUR columns); machinery interest split is a later module</t>
         </is>
       </c>
     </row>
@@ -12648,7 +14062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14048,7 +15462,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>TT_Amount|TT_Amount_Expense_Type|TT_Account|TT_INVOICE_NO|TT_DESCRIPTION|TT_Invoice_Voucher_No|TT_Payment_Number|TT_Clear_Transaction|COMMISION_TT|COMMISION_TT_Expense_Type|COMMISION_TT_Acount|COMMISION_TT_INVOICE_NO|COMMISION_TT_DESCRIPTION|COMMISION_TT_Invoice_Voucher_No|COMMISION_TT_Payment_Number|COMMISION_TT_Clear_Transaction</t>
+          <t>TT_Amount|TT_Amount_Expense_Type|TT_Account</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -14075,7 +15489,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>GRN_NUMBER|REMITTED_AMOUNT|INT_AMOUNT|Match_Invoice_No</t>
+          <t>GRN_NUMBER|REMITTED_AMOUNT|INT_AMOUNT|EXCISE_AMOUNT|Match_Invoice_No</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -14507,7 +15921,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>LC ISSUANCE COMMISSION=&gt;LC ISSUANCE COMMISSION|LC AMENDMENT COMMISSION=&gt;LC AMENDMENT COMMISSION|ACCEPTANCE COMMISSION=&gt;ACCEPTANCE COMMISSION CHARGE</t>
+          <t>LC ISSUANCE COMMISSION=&gt;LC ISSUANCE COMMISSION|LC AMENDMENT COMMISSION=&gt;LC AMENDMENT COMMISSION|ACCEPTANCE COMMISSION=&gt;ACCEPTANCE COMMISSION CHARGE|PRINCIPAL LIQUIDATION=&gt;PRINCIPAL LIQUIDATION</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -14532,7 +15946,11 @@
           <t>LC_Number_Regex</t>
         </is>
       </c>
-      <c r="C70" s="4" t="n"/>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>^5\d{9}$</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>later</t>
@@ -14823,7 +16241,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14850,7 +16268,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14861,6 +16279,411 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>Days after the statement date searched for the advice mail (0 = same day). Not used by SCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Adv_LC_Regex</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>(?:LC NO\s*:|LC REF)\s*([0-9A-Za-z\-]+)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CITI advice reader</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LC number on the CITI advice: "LC NO : 5634610197" or "... LC REF 5634611205" in OTHER INSTRUCTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Adv_Principal_Regex</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PRINCIPAL LIQUIDATION[^\r\n]*?[A-Z]{3}\s*([\d,]+\.\d+)(?=\s*(?:\r|\n|$))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CITI advice reader</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Principal amount (debited currency) on the REPRESENTING block</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Adv_Interest_Regex</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>INTEREST OF[^\r\n]*?[A-Z]{3}\s*([\d,]+\.\d+)(?=\s*(?:\r|\n|$))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CITI advice reader</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Interest amount (debited currency) on the REPRESENTING block</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Adv_Excise_Regex</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EXCISE DUTY OF[^\r\n]*?[A-Z]{3}\s*([\d,]+\.\d+)(?=\s*(?:\r|\n|$))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CITI advice reader</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Excise duty amount (debited currency) on the REPRESENTING block</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Rename_INT_AMOUNT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CITI only: header shown in the output for INT_AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OUTPUT_COLUMNS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Rename_EXCISE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Excise Duty</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Advice_pdf</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>CITI only: header shown in the output for EXCISE_AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Adv_Block_Start</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>REPRESENTING</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Text that starts the charge block of the advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Adv_Block_End</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TOTAL AMOUNT DEBITED</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Text that ends the charge block of the advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Adv_Inline_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[A-Z]{3}\s*([\d,]+\.\d+)\s*$</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Amount at the end of a label line, e.g. INTEREST OF USD146.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Adv_Alone_Amount_Regex</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>^[A-Z]{3}\s*([\d,]+\.\d+)$</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Amount alone on a line, listed after the labels (read in label order)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Adv_Principal_Label</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PRINCIPAL LIQUIDATION</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Advice line label for the principal</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Adv_Interest_Label</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>INTEREST OF</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Advice line label for the interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ADVICE_TEXT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Adv_Excise_Label</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EXCISE DUTY OF</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Advice line label for the excise duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Skip_Marker</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NEEDS DECISION</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Text in the CITI sheet Review column that makes the reader skip the event</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Eur_Bill_Currency</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CITI_advice_reader</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Bill currency that also fills the EUR columns</t>
         </is>
       </c>
     </row>
